--- a/ig/main/ValueSet-fr-core-vs-contact-relationship.xlsx
+++ b/ig/main/ValueSet-fr-core-vs-contact-relationship.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T11:48:42+00:00</t>
+    <t>2024-02-12T13:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-vs-contact-relationship.xlsx
+++ b/ig/main/ValueSet-fr-core-vs-contact-relationship.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T13:27:08+00:00</t>
+    <t>2024-02-12T14:02:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-vs-contact-relationship.xlsx
+++ b/ig/main/ValueSet-fr-core-vs-contact-relationship.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>2.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T14:02:40+00:00</t>
+    <t>2024-02-26T11:03:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-vs-contact-relationship.xlsx
+++ b/ig/main/ValueSet-fr-core-vs-contact-relationship.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-26T11:03:57+00:00</t>
+    <t>2024-03-04T10:55:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-vs-contact-relationship.xlsx
+++ b/ig/main/ValueSet-fr-core-vs-contact-relationship.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-04T10:55:37+00:00</t>
+    <t>2024-03-11T09:42:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-vs-contact-relationship.xlsx
+++ b/ig/main/ValueSet-fr-core-vs-contact-relationship.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-11T09:42:54+00:00</t>
+    <t>2024-03-11T10:34:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-vs-contact-relationship.xlsx
+++ b/ig/main/ValueSet-fr-core-vs-contact-relationship.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-11T10:34:02+00:00</t>
+    <t>2024-03-20T14:49:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-fr-core-vs-contact-relationship.xlsx
+++ b/ig/main/ValueSet-fr-core-vs-contact-relationship.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-20T14:49:36+00:00</t>
+    <t>2024-03-21T08:11:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
